--- a/Data/EC/NIT-9008903845.xlsx
+++ b/Data/EC/NIT-9008903845.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Laura Wilches\Documents\2_ Macro Comfenalco Cartagena\Macro Aviso Incumplimiento y demás\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Operaciones\OneDrive - NIYARAKY COLOMBIA SAS OLD2\Escritorio\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DAE2E9CC-3EB6-4939-914C-D8F45BE8E296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D382A160-0C99-4E10-888E-5278030FCD3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{057C0051-7F71-4E78-906A-3FD88F8130E3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{058D3C0F-5BB8-4B1F-9098-9FF9B007E1C2}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -671,22 +671,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>633769</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>55950</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>437794</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>125025</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D0B54E0-272E-2EC3-FA9F-804DFF50CDD8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED429104-272F-5D61-0CE1-31661EDC554E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -695,7 +695,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -708,7 +708,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="890944" y="236925"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1037,23 +1037,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDED7A7C-5C85-47DC-8690-406451891D56}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{614BE3BA-47DD-4542-989D-F7443A078B11}">
   <dimension ref="B2:J251"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.59765625" customWidth="1"/>
-    <col min="2" max="2" width="18.9296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.1328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.73046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
@@ -1066,7 +1066,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -1077,7 +1077,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -1088,7 +1088,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -1099,8 +1099,8 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>79</v>
       </c>
@@ -1115,8 +1115,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1131,8 +1131,8 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
         <v>80</v>
       </c>
@@ -1147,8 +1147,8 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
         <v>81</v>
       </c>
@@ -1167,7 +1167,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1196,7 +1196,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1219,7 +1219,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1242,7 +1242,7 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1265,7 +1265,7 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
@@ -1288,7 +1288,7 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
@@ -1311,7 +1311,7 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
@@ -1334,7 +1334,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1357,7 +1357,7 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
@@ -1380,7 +1380,7 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
@@ -1403,7 +1403,7 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
@@ -1426,7 +1426,7 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
@@ -1449,7 +1449,7 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
@@ -1472,7 +1472,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
@@ -1495,7 +1495,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1518,7 +1518,7 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
@@ -1541,7 +1541,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
@@ -1564,7 +1564,7 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
@@ -1587,7 +1587,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
@@ -1610,7 +1610,7 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
@@ -1633,7 +1633,7 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
@@ -1656,7 +1656,7 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
@@ -1679,7 +1679,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
@@ -1702,7 +1702,7 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
@@ -1725,7 +1725,7 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
@@ -1748,7 +1748,7 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
@@ -1771,7 +1771,7 @@
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
@@ -1794,7 +1794,7 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
@@ -1817,7 +1817,7 @@
       <c r="I42" s="19"/>
       <c r="J42" s="20"/>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
@@ -1840,7 +1840,7 @@
       <c r="I43" s="19"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
@@ -1863,7 +1863,7 @@
       <c r="I44" s="19"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>8</v>
       </c>
@@ -1886,7 +1886,7 @@
       <c r="I45" s="19"/>
       <c r="J45" s="20"/>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
         <v>8</v>
       </c>
@@ -1909,7 +1909,7 @@
       <c r="I46" s="19"/>
       <c r="J46" s="20"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
@@ -1932,7 +1932,7 @@
       <c r="I47" s="19"/>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
         <v>8</v>
       </c>
@@ -1955,7 +1955,7 @@
       <c r="I48" s="19"/>
       <c r="J48" s="20"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>8</v>
       </c>
@@ -1978,7 +1978,7 @@
       <c r="I49" s="19"/>
       <c r="J49" s="20"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>8</v>
       </c>
@@ -2001,7 +2001,7 @@
       <c r="I50" s="19"/>
       <c r="J50" s="20"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
         <v>8</v>
       </c>
@@ -2024,7 +2024,7 @@
       <c r="I51" s="19"/>
       <c r="J51" s="20"/>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
         <v>8</v>
       </c>
@@ -2047,7 +2047,7 @@
       <c r="I52" s="19"/>
       <c r="J52" s="20"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
         <v>8</v>
       </c>
@@ -2070,7 +2070,7 @@
       <c r="I53" s="19"/>
       <c r="J53" s="20"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>8</v>
       </c>
@@ -2093,7 +2093,7 @@
       <c r="I54" s="19"/>
       <c r="J54" s="20"/>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="15" t="s">
         <v>8</v>
       </c>
@@ -2116,7 +2116,7 @@
       <c r="I55" s="19"/>
       <c r="J55" s="20"/>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" s="15" t="s">
         <v>8</v>
       </c>
@@ -2139,7 +2139,7 @@
       <c r="I56" s="19"/>
       <c r="J56" s="20"/>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="15" t="s">
         <v>8</v>
       </c>
@@ -2162,7 +2162,7 @@
       <c r="I57" s="19"/>
       <c r="J57" s="20"/>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
         <v>8</v>
       </c>
@@ -2185,7 +2185,7 @@
       <c r="I58" s="19"/>
       <c r="J58" s="20"/>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="15" t="s">
         <v>8</v>
       </c>
@@ -2208,7 +2208,7 @@
       <c r="I59" s="19"/>
       <c r="J59" s="20"/>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60" s="15" t="s">
         <v>8</v>
       </c>
@@ -2231,7 +2231,7 @@
       <c r="I60" s="19"/>
       <c r="J60" s="20"/>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61" s="15" t="s">
         <v>8</v>
       </c>
@@ -2254,7 +2254,7 @@
       <c r="I61" s="19"/>
       <c r="J61" s="20"/>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" s="15" t="s">
         <v>8</v>
       </c>
@@ -2277,7 +2277,7 @@
       <c r="I62" s="19"/>
       <c r="J62" s="20"/>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" s="15" t="s">
         <v>8</v>
       </c>
@@ -2300,7 +2300,7 @@
       <c r="I63" s="19"/>
       <c r="J63" s="20"/>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="15" t="s">
         <v>8</v>
       </c>
@@ -2323,7 +2323,7 @@
       <c r="I64" s="19"/>
       <c r="J64" s="20"/>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="15" t="s">
         <v>8</v>
       </c>
@@ -2346,7 +2346,7 @@
       <c r="I65" s="19"/>
       <c r="J65" s="20"/>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="15" t="s">
         <v>8</v>
       </c>
@@ -2369,7 +2369,7 @@
       <c r="I66" s="19"/>
       <c r="J66" s="20"/>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="15" t="s">
         <v>8</v>
       </c>
@@ -2392,7 +2392,7 @@
       <c r="I67" s="19"/>
       <c r="J67" s="20"/>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="15" t="s">
         <v>8</v>
       </c>
@@ -2415,7 +2415,7 @@
       <c r="I68" s="19"/>
       <c r="J68" s="20"/>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="15" t="s">
         <v>8</v>
       </c>
@@ -2438,7 +2438,7 @@
       <c r="I69" s="19"/>
       <c r="J69" s="20"/>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="15" t="s">
         <v>8</v>
       </c>
@@ -2461,7 +2461,7 @@
       <c r="I70" s="19"/>
       <c r="J70" s="20"/>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" s="15" t="s">
         <v>8</v>
       </c>
@@ -2484,7 +2484,7 @@
       <c r="I71" s="19"/>
       <c r="J71" s="20"/>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B72" s="15" t="s">
         <v>8</v>
       </c>
@@ -2507,7 +2507,7 @@
       <c r="I72" s="19"/>
       <c r="J72" s="20"/>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="15" t="s">
         <v>8</v>
       </c>
@@ -2530,7 +2530,7 @@
       <c r="I73" s="19"/>
       <c r="J73" s="20"/>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="15" t="s">
         <v>8</v>
       </c>
@@ -2553,7 +2553,7 @@
       <c r="I74" s="19"/>
       <c r="J74" s="20"/>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="15" t="s">
         <v>8</v>
       </c>
@@ -2576,7 +2576,7 @@
       <c r="I75" s="19"/>
       <c r="J75" s="20"/>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="15" t="s">
         <v>8</v>
       </c>
@@ -2599,7 +2599,7 @@
       <c r="I76" s="19"/>
       <c r="J76" s="20"/>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B77" s="15" t="s">
         <v>8</v>
       </c>
@@ -2622,7 +2622,7 @@
       <c r="I77" s="19"/>
       <c r="J77" s="20"/>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B78" s="15" t="s">
         <v>8</v>
       </c>
@@ -2645,7 +2645,7 @@
       <c r="I78" s="19"/>
       <c r="J78" s="20"/>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B79" s="15" t="s">
         <v>8</v>
       </c>
@@ -2668,7 +2668,7 @@
       <c r="I79" s="19"/>
       <c r="J79" s="20"/>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B80" s="15" t="s">
         <v>8</v>
       </c>
@@ -2691,7 +2691,7 @@
       <c r="I80" s="19"/>
       <c r="J80" s="20"/>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B81" s="15" t="s">
         <v>8</v>
       </c>
@@ -2714,7 +2714,7 @@
       <c r="I81" s="19"/>
       <c r="J81" s="20"/>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" s="15" t="s">
         <v>8</v>
       </c>
@@ -2737,7 +2737,7 @@
       <c r="I82" s="19"/>
       <c r="J82" s="20"/>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" s="15" t="s">
         <v>8</v>
       </c>
@@ -2760,7 +2760,7 @@
       <c r="I83" s="19"/>
       <c r="J83" s="20"/>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B84" s="15" t="s">
         <v>8</v>
       </c>
@@ -2783,7 +2783,7 @@
       <c r="I84" s="19"/>
       <c r="J84" s="20"/>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B85" s="15" t="s">
         <v>8</v>
       </c>
@@ -2806,7 +2806,7 @@
       <c r="I85" s="19"/>
       <c r="J85" s="20"/>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B86" s="15" t="s">
         <v>8</v>
       </c>
@@ -2829,7 +2829,7 @@
       <c r="I86" s="19"/>
       <c r="J86" s="20"/>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B87" s="15" t="s">
         <v>8</v>
       </c>
@@ -2852,7 +2852,7 @@
       <c r="I87" s="19"/>
       <c r="J87" s="20"/>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B88" s="15" t="s">
         <v>8</v>
       </c>
@@ -2875,7 +2875,7 @@
       <c r="I88" s="19"/>
       <c r="J88" s="20"/>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B89" s="15" t="s">
         <v>8</v>
       </c>
@@ -2898,7 +2898,7 @@
       <c r="I89" s="19"/>
       <c r="J89" s="20"/>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B90" s="15" t="s">
         <v>8</v>
       </c>
@@ -2921,7 +2921,7 @@
       <c r="I90" s="19"/>
       <c r="J90" s="20"/>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B91" s="15" t="s">
         <v>8</v>
       </c>
@@ -2944,7 +2944,7 @@
       <c r="I91" s="19"/>
       <c r="J91" s="20"/>
     </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B92" s="15" t="s">
         <v>8</v>
       </c>
@@ -2967,7 +2967,7 @@
       <c r="I92" s="19"/>
       <c r="J92" s="20"/>
     </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B93" s="15" t="s">
         <v>8</v>
       </c>
@@ -2990,7 +2990,7 @@
       <c r="I93" s="19"/>
       <c r="J93" s="20"/>
     </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B94" s="15" t="s">
         <v>8</v>
       </c>
@@ -3013,7 +3013,7 @@
       <c r="I94" s="19"/>
       <c r="J94" s="20"/>
     </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B95" s="15" t="s">
         <v>8</v>
       </c>
@@ -3036,7 +3036,7 @@
       <c r="I95" s="19"/>
       <c r="J95" s="20"/>
     </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B96" s="15" t="s">
         <v>8</v>
       </c>
@@ -3059,7 +3059,7 @@
       <c r="I96" s="19"/>
       <c r="J96" s="20"/>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B97" s="15" t="s">
         <v>8</v>
       </c>
@@ -3082,7 +3082,7 @@
       <c r="I97" s="19"/>
       <c r="J97" s="20"/>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B98" s="15" t="s">
         <v>8</v>
       </c>
@@ -3105,7 +3105,7 @@
       <c r="I98" s="19"/>
       <c r="J98" s="20"/>
     </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B99" s="15" t="s">
         <v>8</v>
       </c>
@@ -3128,7 +3128,7 @@
       <c r="I99" s="19"/>
       <c r="J99" s="20"/>
     </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B100" s="15" t="s">
         <v>8</v>
       </c>
@@ -3151,7 +3151,7 @@
       <c r="I100" s="19"/>
       <c r="J100" s="20"/>
     </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B101" s="15" t="s">
         <v>8</v>
       </c>
@@ -3174,7 +3174,7 @@
       <c r="I101" s="19"/>
       <c r="J101" s="20"/>
     </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="102" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B102" s="15" t="s">
         <v>8</v>
       </c>
@@ -3197,7 +3197,7 @@
       <c r="I102" s="19"/>
       <c r="J102" s="20"/>
     </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B103" s="15" t="s">
         <v>8</v>
       </c>
@@ -3220,7 +3220,7 @@
       <c r="I103" s="19"/>
       <c r="J103" s="20"/>
     </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="104" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B104" s="15" t="s">
         <v>8</v>
       </c>
@@ -3243,7 +3243,7 @@
       <c r="I104" s="19"/>
       <c r="J104" s="20"/>
     </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="105" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B105" s="15" t="s">
         <v>8</v>
       </c>
@@ -3266,7 +3266,7 @@
       <c r="I105" s="19"/>
       <c r="J105" s="20"/>
     </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="106" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B106" s="15" t="s">
         <v>8</v>
       </c>
@@ -3289,7 +3289,7 @@
       <c r="I106" s="19"/>
       <c r="J106" s="20"/>
     </row>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="107" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B107" s="15" t="s">
         <v>8</v>
       </c>
@@ -3312,7 +3312,7 @@
       <c r="I107" s="19"/>
       <c r="J107" s="20"/>
     </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="108" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B108" s="15" t="s">
         <v>8</v>
       </c>
@@ -3335,7 +3335,7 @@
       <c r="I108" s="19"/>
       <c r="J108" s="20"/>
     </row>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="109" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B109" s="15" t="s">
         <v>8</v>
       </c>
@@ -3358,7 +3358,7 @@
       <c r="I109" s="19"/>
       <c r="J109" s="20"/>
     </row>
-    <row r="110" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="110" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B110" s="15" t="s">
         <v>8</v>
       </c>
@@ -3381,7 +3381,7 @@
       <c r="I110" s="19"/>
       <c r="J110" s="20"/>
     </row>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="111" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B111" s="15" t="s">
         <v>8</v>
       </c>
@@ -3404,7 +3404,7 @@
       <c r="I111" s="19"/>
       <c r="J111" s="20"/>
     </row>
-    <row r="112" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="112" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B112" s="15" t="s">
         <v>8</v>
       </c>
@@ -3427,7 +3427,7 @@
       <c r="I112" s="19"/>
       <c r="J112" s="20"/>
     </row>
-    <row r="113" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="113" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B113" s="15" t="s">
         <v>8</v>
       </c>
@@ -3450,7 +3450,7 @@
       <c r="I113" s="19"/>
       <c r="J113" s="20"/>
     </row>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="114" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B114" s="15" t="s">
         <v>8</v>
       </c>
@@ -3473,7 +3473,7 @@
       <c r="I114" s="19"/>
       <c r="J114" s="20"/>
     </row>
-    <row r="115" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="115" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B115" s="15" t="s">
         <v>8</v>
       </c>
@@ -3496,7 +3496,7 @@
       <c r="I115" s="19"/>
       <c r="J115" s="20"/>
     </row>
-    <row r="116" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="116" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B116" s="15" t="s">
         <v>8</v>
       </c>
@@ -3519,7 +3519,7 @@
       <c r="I116" s="19"/>
       <c r="J116" s="20"/>
     </row>
-    <row r="117" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="117" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B117" s="15" t="s">
         <v>8</v>
       </c>
@@ -3542,7 +3542,7 @@
       <c r="I117" s="19"/>
       <c r="J117" s="20"/>
     </row>
-    <row r="118" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="118" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B118" s="15" t="s">
         <v>8</v>
       </c>
@@ -3565,7 +3565,7 @@
       <c r="I118" s="19"/>
       <c r="J118" s="20"/>
     </row>
-    <row r="119" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="119" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B119" s="15" t="s">
         <v>8</v>
       </c>
@@ -3588,7 +3588,7 @@
       <c r="I119" s="19"/>
       <c r="J119" s="20"/>
     </row>
-    <row r="120" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="120" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B120" s="15" t="s">
         <v>8</v>
       </c>
@@ -3611,7 +3611,7 @@
       <c r="I120" s="19"/>
       <c r="J120" s="20"/>
     </row>
-    <row r="121" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="121" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B121" s="15" t="s">
         <v>8</v>
       </c>
@@ -3634,7 +3634,7 @@
       <c r="I121" s="19"/>
       <c r="J121" s="20"/>
     </row>
-    <row r="122" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="122" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B122" s="15" t="s">
         <v>8</v>
       </c>
@@ -3657,7 +3657,7 @@
       <c r="I122" s="19"/>
       <c r="J122" s="20"/>
     </row>
-    <row r="123" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="123" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B123" s="15" t="s">
         <v>8</v>
       </c>
@@ -3680,7 +3680,7 @@
       <c r="I123" s="19"/>
       <c r="J123" s="20"/>
     </row>
-    <row r="124" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="124" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B124" s="15" t="s">
         <v>8</v>
       </c>
@@ -3703,7 +3703,7 @@
       <c r="I124" s="19"/>
       <c r="J124" s="20"/>
     </row>
-    <row r="125" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="125" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B125" s="15" t="s">
         <v>8</v>
       </c>
@@ -3726,7 +3726,7 @@
       <c r="I125" s="19"/>
       <c r="J125" s="20"/>
     </row>
-    <row r="126" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="126" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B126" s="15" t="s">
         <v>8</v>
       </c>
@@ -3749,7 +3749,7 @@
       <c r="I126" s="19"/>
       <c r="J126" s="20"/>
     </row>
-    <row r="127" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="127" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B127" s="15" t="s">
         <v>8</v>
       </c>
@@ -3772,7 +3772,7 @@
       <c r="I127" s="19"/>
       <c r="J127" s="20"/>
     </row>
-    <row r="128" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="128" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B128" s="15" t="s">
         <v>8</v>
       </c>
@@ -3795,7 +3795,7 @@
       <c r="I128" s="19"/>
       <c r="J128" s="20"/>
     </row>
-    <row r="129" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="129" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B129" s="15" t="s">
         <v>8</v>
       </c>
@@ -3818,7 +3818,7 @@
       <c r="I129" s="19"/>
       <c r="J129" s="20"/>
     </row>
-    <row r="130" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="130" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B130" s="15" t="s">
         <v>8</v>
       </c>
@@ -3841,7 +3841,7 @@
       <c r="I130" s="19"/>
       <c r="J130" s="20"/>
     </row>
-    <row r="131" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="131" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B131" s="15" t="s">
         <v>8</v>
       </c>
@@ -3864,7 +3864,7 @@
       <c r="I131" s="19"/>
       <c r="J131" s="20"/>
     </row>
-    <row r="132" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="132" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B132" s="15" t="s">
         <v>8</v>
       </c>
@@ -3887,7 +3887,7 @@
       <c r="I132" s="19"/>
       <c r="J132" s="20"/>
     </row>
-    <row r="133" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="133" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B133" s="15" t="s">
         <v>8</v>
       </c>
@@ -3910,7 +3910,7 @@
       <c r="I133" s="19"/>
       <c r="J133" s="20"/>
     </row>
-    <row r="134" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="134" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B134" s="15" t="s">
         <v>8</v>
       </c>
@@ -3933,7 +3933,7 @@
       <c r="I134" s="19"/>
       <c r="J134" s="20"/>
     </row>
-    <row r="135" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="135" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B135" s="15" t="s">
         <v>8</v>
       </c>
@@ -3956,7 +3956,7 @@
       <c r="I135" s="19"/>
       <c r="J135" s="20"/>
     </row>
-    <row r="136" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="136" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B136" s="15" t="s">
         <v>8</v>
       </c>
@@ -3979,7 +3979,7 @@
       <c r="I136" s="19"/>
       <c r="J136" s="20"/>
     </row>
-    <row r="137" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="137" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B137" s="15" t="s">
         <v>8</v>
       </c>
@@ -4002,7 +4002,7 @@
       <c r="I137" s="19"/>
       <c r="J137" s="20"/>
     </row>
-    <row r="138" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="138" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B138" s="15" t="s">
         <v>8</v>
       </c>
@@ -4025,7 +4025,7 @@
       <c r="I138" s="19"/>
       <c r="J138" s="20"/>
     </row>
-    <row r="139" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="139" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B139" s="15" t="s">
         <v>8</v>
       </c>
@@ -4048,7 +4048,7 @@
       <c r="I139" s="19"/>
       <c r="J139" s="20"/>
     </row>
-    <row r="140" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="140" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B140" s="15" t="s">
         <v>8</v>
       </c>
@@ -4071,7 +4071,7 @@
       <c r="I140" s="19"/>
       <c r="J140" s="20"/>
     </row>
-    <row r="141" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="141" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B141" s="15" t="s">
         <v>8</v>
       </c>
@@ -4094,7 +4094,7 @@
       <c r="I141" s="19"/>
       <c r="J141" s="20"/>
     </row>
-    <row r="142" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="142" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B142" s="15" t="s">
         <v>8</v>
       </c>
@@ -4117,7 +4117,7 @@
       <c r="I142" s="19"/>
       <c r="J142" s="20"/>
     </row>
-    <row r="143" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="143" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B143" s="15" t="s">
         <v>8</v>
       </c>
@@ -4140,7 +4140,7 @@
       <c r="I143" s="19"/>
       <c r="J143" s="20"/>
     </row>
-    <row r="144" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="144" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B144" s="15" t="s">
         <v>8</v>
       </c>
@@ -4163,7 +4163,7 @@
       <c r="I144" s="19"/>
       <c r="J144" s="20"/>
     </row>
-    <row r="145" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="145" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B145" s="15" t="s">
         <v>8</v>
       </c>
@@ -4186,7 +4186,7 @@
       <c r="I145" s="19"/>
       <c r="J145" s="20"/>
     </row>
-    <row r="146" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="146" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B146" s="15" t="s">
         <v>8</v>
       </c>
@@ -4209,7 +4209,7 @@
       <c r="I146" s="19"/>
       <c r="J146" s="20"/>
     </row>
-    <row r="147" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="147" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B147" s="15" t="s">
         <v>8</v>
       </c>
@@ -4232,7 +4232,7 @@
       <c r="I147" s="19"/>
       <c r="J147" s="20"/>
     </row>
-    <row r="148" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="148" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B148" s="15" t="s">
         <v>8</v>
       </c>
@@ -4255,7 +4255,7 @@
       <c r="I148" s="19"/>
       <c r="J148" s="20"/>
     </row>
-    <row r="149" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="149" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B149" s="15" t="s">
         <v>8</v>
       </c>
@@ -4278,7 +4278,7 @@
       <c r="I149" s="19"/>
       <c r="J149" s="20"/>
     </row>
-    <row r="150" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="150" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B150" s="15" t="s">
         <v>8</v>
       </c>
@@ -4301,7 +4301,7 @@
       <c r="I150" s="19"/>
       <c r="J150" s="20"/>
     </row>
-    <row r="151" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="151" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B151" s="15" t="s">
         <v>8</v>
       </c>
@@ -4324,7 +4324,7 @@
       <c r="I151" s="19"/>
       <c r="J151" s="20"/>
     </row>
-    <row r="152" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="152" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B152" s="15" t="s">
         <v>8</v>
       </c>
@@ -4347,7 +4347,7 @@
       <c r="I152" s="19"/>
       <c r="J152" s="20"/>
     </row>
-    <row r="153" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="153" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B153" s="15" t="s">
         <v>8</v>
       </c>
@@ -4370,7 +4370,7 @@
       <c r="I153" s="19"/>
       <c r="J153" s="20"/>
     </row>
-    <row r="154" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="154" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B154" s="15" t="s">
         <v>8</v>
       </c>
@@ -4393,7 +4393,7 @@
       <c r="I154" s="19"/>
       <c r="J154" s="20"/>
     </row>
-    <row r="155" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="155" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B155" s="15" t="s">
         <v>8</v>
       </c>
@@ -4416,7 +4416,7 @@
       <c r="I155" s="19"/>
       <c r="J155" s="20"/>
     </row>
-    <row r="156" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="156" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B156" s="15" t="s">
         <v>8</v>
       </c>
@@ -4439,7 +4439,7 @@
       <c r="I156" s="19"/>
       <c r="J156" s="20"/>
     </row>
-    <row r="157" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="157" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B157" s="15" t="s">
         <v>8</v>
       </c>
@@ -4462,7 +4462,7 @@
       <c r="I157" s="19"/>
       <c r="J157" s="20"/>
     </row>
-    <row r="158" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="158" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B158" s="15" t="s">
         <v>8</v>
       </c>
@@ -4485,7 +4485,7 @@
       <c r="I158" s="19"/>
       <c r="J158" s="20"/>
     </row>
-    <row r="159" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="159" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B159" s="15" t="s">
         <v>8</v>
       </c>
@@ -4508,7 +4508,7 @@
       <c r="I159" s="19"/>
       <c r="J159" s="20"/>
     </row>
-    <row r="160" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="160" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B160" s="15" t="s">
         <v>8</v>
       </c>
@@ -4531,7 +4531,7 @@
       <c r="I160" s="19"/>
       <c r="J160" s="20"/>
     </row>
-    <row r="161" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="161" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B161" s="15" t="s">
         <v>8</v>
       </c>
@@ -4554,7 +4554,7 @@
       <c r="I161" s="19"/>
       <c r="J161" s="20"/>
     </row>
-    <row r="162" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="162" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B162" s="15" t="s">
         <v>8</v>
       </c>
@@ -4577,7 +4577,7 @@
       <c r="I162" s="19"/>
       <c r="J162" s="20"/>
     </row>
-    <row r="163" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="163" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B163" s="15" t="s">
         <v>8</v>
       </c>
@@ -4600,7 +4600,7 @@
       <c r="I163" s="19"/>
       <c r="J163" s="20"/>
     </row>
-    <row r="164" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="164" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B164" s="15" t="s">
         <v>8</v>
       </c>
@@ -4623,7 +4623,7 @@
       <c r="I164" s="19"/>
       <c r="J164" s="20"/>
     </row>
-    <row r="165" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="165" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B165" s="15" t="s">
         <v>8</v>
       </c>
@@ -4646,7 +4646,7 @@
       <c r="I165" s="19"/>
       <c r="J165" s="20"/>
     </row>
-    <row r="166" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="166" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B166" s="15" t="s">
         <v>8</v>
       </c>
@@ -4669,7 +4669,7 @@
       <c r="I166" s="19"/>
       <c r="J166" s="20"/>
     </row>
-    <row r="167" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="167" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B167" s="15" t="s">
         <v>8</v>
       </c>
@@ -4692,7 +4692,7 @@
       <c r="I167" s="19"/>
       <c r="J167" s="20"/>
     </row>
-    <row r="168" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="168" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B168" s="15" t="s">
         <v>8</v>
       </c>
@@ -4715,7 +4715,7 @@
       <c r="I168" s="19"/>
       <c r="J168" s="20"/>
     </row>
-    <row r="169" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="169" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B169" s="15" t="s">
         <v>8</v>
       </c>
@@ -4738,7 +4738,7 @@
       <c r="I169" s="19"/>
       <c r="J169" s="20"/>
     </row>
-    <row r="170" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="170" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B170" s="15" t="s">
         <v>8</v>
       </c>
@@ -4761,7 +4761,7 @@
       <c r="I170" s="19"/>
       <c r="J170" s="20"/>
     </row>
-    <row r="171" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="171" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B171" s="15" t="s">
         <v>8</v>
       </c>
@@ -4784,7 +4784,7 @@
       <c r="I171" s="19"/>
       <c r="J171" s="20"/>
     </row>
-    <row r="172" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="172" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B172" s="15" t="s">
         <v>8</v>
       </c>
@@ -4807,7 +4807,7 @@
       <c r="I172" s="19"/>
       <c r="J172" s="20"/>
     </row>
-    <row r="173" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="173" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B173" s="15" t="s">
         <v>8</v>
       </c>
@@ -4830,7 +4830,7 @@
       <c r="I173" s="19"/>
       <c r="J173" s="20"/>
     </row>
-    <row r="174" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="174" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B174" s="15" t="s">
         <v>8</v>
       </c>
@@ -4853,7 +4853,7 @@
       <c r="I174" s="19"/>
       <c r="J174" s="20"/>
     </row>
-    <row r="175" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="175" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B175" s="15" t="s">
         <v>8</v>
       </c>
@@ -4876,7 +4876,7 @@
       <c r="I175" s="19"/>
       <c r="J175" s="20"/>
     </row>
-    <row r="176" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="176" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B176" s="15" t="s">
         <v>8</v>
       </c>
@@ -4899,7 +4899,7 @@
       <c r="I176" s="19"/>
       <c r="J176" s="20"/>
     </row>
-    <row r="177" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="177" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B177" s="15" t="s">
         <v>8</v>
       </c>
@@ -4922,7 +4922,7 @@
       <c r="I177" s="19"/>
       <c r="J177" s="20"/>
     </row>
-    <row r="178" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="178" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B178" s="15" t="s">
         <v>8</v>
       </c>
@@ -4945,7 +4945,7 @@
       <c r="I178" s="19"/>
       <c r="J178" s="20"/>
     </row>
-    <row r="179" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="179" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B179" s="15" t="s">
         <v>8</v>
       </c>
@@ -4968,7 +4968,7 @@
       <c r="I179" s="19"/>
       <c r="J179" s="20"/>
     </row>
-    <row r="180" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="180" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B180" s="15" t="s">
         <v>8</v>
       </c>
@@ -4991,7 +4991,7 @@
       <c r="I180" s="19"/>
       <c r="J180" s="20"/>
     </row>
-    <row r="181" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="181" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B181" s="15" t="s">
         <v>8</v>
       </c>
@@ -5014,7 +5014,7 @@
       <c r="I181" s="19"/>
       <c r="J181" s="20"/>
     </row>
-    <row r="182" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="182" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B182" s="15" t="s">
         <v>8</v>
       </c>
@@ -5037,7 +5037,7 @@
       <c r="I182" s="19"/>
       <c r="J182" s="20"/>
     </row>
-    <row r="183" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="183" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B183" s="15" t="s">
         <v>8</v>
       </c>
@@ -5060,7 +5060,7 @@
       <c r="I183" s="19"/>
       <c r="J183" s="20"/>
     </row>
-    <row r="184" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="184" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B184" s="15" t="s">
         <v>8</v>
       </c>
@@ -5083,7 +5083,7 @@
       <c r="I184" s="19"/>
       <c r="J184" s="20"/>
     </row>
-    <row r="185" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="185" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B185" s="15" t="s">
         <v>8</v>
       </c>
@@ -5106,7 +5106,7 @@
       <c r="I185" s="19"/>
       <c r="J185" s="20"/>
     </row>
-    <row r="186" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="186" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B186" s="15" t="s">
         <v>8</v>
       </c>
@@ -5129,7 +5129,7 @@
       <c r="I186" s="19"/>
       <c r="J186" s="20"/>
     </row>
-    <row r="187" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="187" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B187" s="15" t="s">
         <v>8</v>
       </c>
@@ -5152,7 +5152,7 @@
       <c r="I187" s="19"/>
       <c r="J187" s="20"/>
     </row>
-    <row r="188" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="188" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B188" s="15" t="s">
         <v>8</v>
       </c>
@@ -5175,7 +5175,7 @@
       <c r="I188" s="19"/>
       <c r="J188" s="20"/>
     </row>
-    <row r="189" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="189" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B189" s="15" t="s">
         <v>8</v>
       </c>
@@ -5198,7 +5198,7 @@
       <c r="I189" s="19"/>
       <c r="J189" s="20"/>
     </row>
-    <row r="190" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="190" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B190" s="15" t="s">
         <v>8</v>
       </c>
@@ -5221,7 +5221,7 @@
       <c r="I190" s="19"/>
       <c r="J190" s="20"/>
     </row>
-    <row r="191" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="191" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B191" s="15" t="s">
         <v>8</v>
       </c>
@@ -5244,7 +5244,7 @@
       <c r="I191" s="19"/>
       <c r="J191" s="20"/>
     </row>
-    <row r="192" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="192" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B192" s="15" t="s">
         <v>8</v>
       </c>
@@ -5267,7 +5267,7 @@
       <c r="I192" s="19"/>
       <c r="J192" s="20"/>
     </row>
-    <row r="193" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="193" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B193" s="15" t="s">
         <v>8</v>
       </c>
@@ -5290,7 +5290,7 @@
       <c r="I193" s="19"/>
       <c r="J193" s="20"/>
     </row>
-    <row r="194" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="194" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B194" s="15" t="s">
         <v>8</v>
       </c>
@@ -5313,7 +5313,7 @@
       <c r="I194" s="19"/>
       <c r="J194" s="20"/>
     </row>
-    <row r="195" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="195" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B195" s="15" t="s">
         <v>8</v>
       </c>
@@ -5336,7 +5336,7 @@
       <c r="I195" s="19"/>
       <c r="J195" s="20"/>
     </row>
-    <row r="196" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="196" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B196" s="15" t="s">
         <v>8</v>
       </c>
@@ -5359,7 +5359,7 @@
       <c r="I196" s="19"/>
       <c r="J196" s="20"/>
     </row>
-    <row r="197" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="197" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B197" s="15" t="s">
         <v>8</v>
       </c>
@@ -5382,7 +5382,7 @@
       <c r="I197" s="19"/>
       <c r="J197" s="20"/>
     </row>
-    <row r="198" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="198" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B198" s="15" t="s">
         <v>8</v>
       </c>
@@ -5405,7 +5405,7 @@
       <c r="I198" s="19"/>
       <c r="J198" s="20"/>
     </row>
-    <row r="199" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="199" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B199" s="15" t="s">
         <v>8</v>
       </c>
@@ -5428,7 +5428,7 @@
       <c r="I199" s="19"/>
       <c r="J199" s="20"/>
     </row>
-    <row r="200" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="200" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B200" s="15" t="s">
         <v>8</v>
       </c>
@@ -5451,7 +5451,7 @@
       <c r="I200" s="19"/>
       <c r="J200" s="20"/>
     </row>
-    <row r="201" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="201" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B201" s="15" t="s">
         <v>8</v>
       </c>
@@ -5474,7 +5474,7 @@
       <c r="I201" s="19"/>
       <c r="J201" s="20"/>
     </row>
-    <row r="202" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="202" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B202" s="15" t="s">
         <v>8</v>
       </c>
@@ -5497,7 +5497,7 @@
       <c r="I202" s="19"/>
       <c r="J202" s="20"/>
     </row>
-    <row r="203" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="203" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B203" s="15" t="s">
         <v>8</v>
       </c>
@@ -5520,7 +5520,7 @@
       <c r="I203" s="19"/>
       <c r="J203" s="20"/>
     </row>
-    <row r="204" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="204" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B204" s="15" t="s">
         <v>8</v>
       </c>
@@ -5543,7 +5543,7 @@
       <c r="I204" s="19"/>
       <c r="J204" s="20"/>
     </row>
-    <row r="205" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="205" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B205" s="15" t="s">
         <v>8</v>
       </c>
@@ -5566,7 +5566,7 @@
       <c r="I205" s="19"/>
       <c r="J205" s="20"/>
     </row>
-    <row r="206" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="206" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B206" s="15" t="s">
         <v>8</v>
       </c>
@@ -5589,7 +5589,7 @@
       <c r="I206" s="19"/>
       <c r="J206" s="20"/>
     </row>
-    <row r="207" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="207" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B207" s="15" t="s">
         <v>8</v>
       </c>
@@ -5612,7 +5612,7 @@
       <c r="I207" s="19"/>
       <c r="J207" s="20"/>
     </row>
-    <row r="208" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="208" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B208" s="15" t="s">
         <v>8</v>
       </c>
@@ -5635,7 +5635,7 @@
       <c r="I208" s="19"/>
       <c r="J208" s="20"/>
     </row>
-    <row r="209" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="209" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B209" s="15" t="s">
         <v>8</v>
       </c>
@@ -5658,7 +5658,7 @@
       <c r="I209" s="19"/>
       <c r="J209" s="20"/>
     </row>
-    <row r="210" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="210" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B210" s="15" t="s">
         <v>8</v>
       </c>
@@ -5681,7 +5681,7 @@
       <c r="I210" s="19"/>
       <c r="J210" s="20"/>
     </row>
-    <row r="211" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="211" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B211" s="15" t="s">
         <v>8</v>
       </c>
@@ -5704,7 +5704,7 @@
       <c r="I211" s="19"/>
       <c r="J211" s="20"/>
     </row>
-    <row r="212" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="212" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B212" s="15" t="s">
         <v>8</v>
       </c>
@@ -5727,7 +5727,7 @@
       <c r="I212" s="19"/>
       <c r="J212" s="20"/>
     </row>
-    <row r="213" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="213" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B213" s="15" t="s">
         <v>8</v>
       </c>
@@ -5750,7 +5750,7 @@
       <c r="I213" s="19"/>
       <c r="J213" s="20"/>
     </row>
-    <row r="214" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="214" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B214" s="15" t="s">
         <v>8</v>
       </c>
@@ -5773,7 +5773,7 @@
       <c r="I214" s="19"/>
       <c r="J214" s="20"/>
     </row>
-    <row r="215" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="215" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B215" s="15" t="s">
         <v>8</v>
       </c>
@@ -5796,7 +5796,7 @@
       <c r="I215" s="19"/>
       <c r="J215" s="20"/>
     </row>
-    <row r="216" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="216" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B216" s="15" t="s">
         <v>8</v>
       </c>
@@ -5819,7 +5819,7 @@
       <c r="I216" s="19"/>
       <c r="J216" s="20"/>
     </row>
-    <row r="217" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="217" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B217" s="15" t="s">
         <v>8</v>
       </c>
@@ -5842,7 +5842,7 @@
       <c r="I217" s="19"/>
       <c r="J217" s="20"/>
     </row>
-    <row r="218" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="218" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B218" s="15" t="s">
         <v>8</v>
       </c>
@@ -5865,7 +5865,7 @@
       <c r="I218" s="19"/>
       <c r="J218" s="20"/>
     </row>
-    <row r="219" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="219" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B219" s="15" t="s">
         <v>8</v>
       </c>
@@ -5888,7 +5888,7 @@
       <c r="I219" s="19"/>
       <c r="J219" s="20"/>
     </row>
-    <row r="220" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="220" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B220" s="15" t="s">
         <v>8</v>
       </c>
@@ -5911,7 +5911,7 @@
       <c r="I220" s="19"/>
       <c r="J220" s="20"/>
     </row>
-    <row r="221" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="221" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B221" s="15" t="s">
         <v>8</v>
       </c>
@@ -5934,7 +5934,7 @@
       <c r="I221" s="19"/>
       <c r="J221" s="20"/>
     </row>
-    <row r="222" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="222" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B222" s="15" t="s">
         <v>8</v>
       </c>
@@ -5957,7 +5957,7 @@
       <c r="I222" s="19"/>
       <c r="J222" s="20"/>
     </row>
-    <row r="223" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="223" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B223" s="15" t="s">
         <v>8</v>
       </c>
@@ -5980,7 +5980,7 @@
       <c r="I223" s="19"/>
       <c r="J223" s="20"/>
     </row>
-    <row r="224" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="224" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B224" s="15" t="s">
         <v>8</v>
       </c>
@@ -6003,7 +6003,7 @@
       <c r="I224" s="19"/>
       <c r="J224" s="20"/>
     </row>
-    <row r="225" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="225" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B225" s="15" t="s">
         <v>8</v>
       </c>
@@ -6026,7 +6026,7 @@
       <c r="I225" s="19"/>
       <c r="J225" s="20"/>
     </row>
-    <row r="226" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="226" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B226" s="15" t="s">
         <v>8</v>
       </c>
@@ -6049,7 +6049,7 @@
       <c r="I226" s="19"/>
       <c r="J226" s="20"/>
     </row>
-    <row r="227" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="227" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B227" s="15" t="s">
         <v>8</v>
       </c>
@@ -6072,7 +6072,7 @@
       <c r="I227" s="19"/>
       <c r="J227" s="20"/>
     </row>
-    <row r="228" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="228" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B228" s="15" t="s">
         <v>8</v>
       </c>
@@ -6095,7 +6095,7 @@
       <c r="I228" s="19"/>
       <c r="J228" s="20"/>
     </row>
-    <row r="229" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="229" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B229" s="15" t="s">
         <v>8</v>
       </c>
@@ -6118,7 +6118,7 @@
       <c r="I229" s="19"/>
       <c r="J229" s="20"/>
     </row>
-    <row r="230" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="230" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B230" s="15" t="s">
         <v>8</v>
       </c>
@@ -6141,7 +6141,7 @@
       <c r="I230" s="19"/>
       <c r="J230" s="20"/>
     </row>
-    <row r="231" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="231" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B231" s="15" t="s">
         <v>8</v>
       </c>
@@ -6164,7 +6164,7 @@
       <c r="I231" s="19"/>
       <c r="J231" s="20"/>
     </row>
-    <row r="232" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="232" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B232" s="15" t="s">
         <v>8</v>
       </c>
@@ -6187,7 +6187,7 @@
       <c r="I232" s="19"/>
       <c r="J232" s="20"/>
     </row>
-    <row r="233" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="233" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B233" s="15" t="s">
         <v>8</v>
       </c>
@@ -6210,7 +6210,7 @@
       <c r="I233" s="19"/>
       <c r="J233" s="20"/>
     </row>
-    <row r="234" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="234" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B234" s="15" t="s">
         <v>8</v>
       </c>
@@ -6233,7 +6233,7 @@
       <c r="I234" s="19"/>
       <c r="J234" s="20"/>
     </row>
-    <row r="235" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="235" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B235" s="15" t="s">
         <v>8</v>
       </c>
@@ -6256,7 +6256,7 @@
       <c r="I235" s="19"/>
       <c r="J235" s="20"/>
     </row>
-    <row r="236" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="236" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B236" s="15" t="s">
         <v>8</v>
       </c>
@@ -6279,7 +6279,7 @@
       <c r="I236" s="19"/>
       <c r="J236" s="20"/>
     </row>
-    <row r="237" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="237" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B237" s="15" t="s">
         <v>8</v>
       </c>
@@ -6302,7 +6302,7 @@
       <c r="I237" s="19"/>
       <c r="J237" s="20"/>
     </row>
-    <row r="238" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="238" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B238" s="15" t="s">
         <v>8</v>
       </c>
@@ -6325,7 +6325,7 @@
       <c r="I238" s="19"/>
       <c r="J238" s="20"/>
     </row>
-    <row r="239" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="239" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B239" s="15" t="s">
         <v>8</v>
       </c>
@@ -6348,7 +6348,7 @@
       <c r="I239" s="19"/>
       <c r="J239" s="20"/>
     </row>
-    <row r="240" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="240" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B240" s="15" t="s">
         <v>8</v>
       </c>
@@ -6371,7 +6371,7 @@
       <c r="I240" s="19"/>
       <c r="J240" s="20"/>
     </row>
-    <row r="241" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="241" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B241" s="15" t="s">
         <v>8</v>
       </c>
@@ -6394,7 +6394,7 @@
       <c r="I241" s="19"/>
       <c r="J241" s="20"/>
     </row>
-    <row r="242" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="242" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B242" s="15" t="s">
         <v>8</v>
       </c>
@@ -6417,7 +6417,7 @@
       <c r="I242" s="19"/>
       <c r="J242" s="20"/>
     </row>
-    <row r="243" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="243" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B243" s="15" t="s">
         <v>8</v>
       </c>
@@ -6440,7 +6440,7 @@
       <c r="I243" s="19"/>
       <c r="J243" s="20"/>
     </row>
-    <row r="244" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="244" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B244" s="15" t="s">
         <v>8</v>
       </c>
@@ -6463,7 +6463,7 @@
       <c r="I244" s="19"/>
       <c r="J244" s="20"/>
     </row>
-    <row r="245" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="245" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B245" s="21" t="s">
         <v>8</v>
       </c>
@@ -6486,7 +6486,7 @@
       <c r="I245" s="25"/>
       <c r="J245" s="26"/>
     </row>
-    <row r="250" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="250" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B250" s="32" t="s">
         <v>87</v>
       </c>
@@ -6497,7 +6497,7 @@
       <c r="I250" s="1"/>
       <c r="J250" s="1"/>
     </row>
-    <row r="251" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="251" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B251" s="32" t="s">
         <v>86</v>
       </c>
